--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N1_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N1_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.19730288191894</v>
+        <v>4.419561718311828</v>
       </c>
       <c r="D2" t="n">
-        <v>26.85024805600738</v>
+        <v>4.3631653091012</v>
       </c>
       <c r="E2" t="n">
-        <v>12.57896621679088</v>
+        <v>2.044082010228518</v>
       </c>
       <c r="F2" t="n">
-        <v>13.02485809901058</v>
+        <v>2.11653944108922</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.46626134344774</v>
+        <v>2.838267468310258</v>
       </c>
       <c r="D3" t="n">
-        <v>17.63064483857972</v>
+        <v>2.864979786269204</v>
       </c>
       <c r="E3" t="n">
-        <v>12.57896621679088</v>
+        <v>2.044082010228518</v>
       </c>
       <c r="F3" t="n">
-        <v>13.02485809901058</v>
+        <v>2.11653944108922</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.1990101905516</v>
+        <v>3.282339155964635</v>
       </c>
       <c r="D4" t="n">
-        <v>19.90138329254313</v>
+        <v>3.233974785038259</v>
       </c>
       <c r="E4" t="n">
-        <v>12.57896621679088</v>
+        <v>2.044082010228518</v>
       </c>
       <c r="F4" t="n">
-        <v>13.02485809901058</v>
+        <v>2.11653944108922</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>54.93171200047257</v>
+        <v>8.926403200076793</v>
       </c>
       <c r="D5" t="n">
-        <v>54.19087935664265</v>
+        <v>8.806017895454431</v>
       </c>
       <c r="E5" t="n">
-        <v>12.57896621679088</v>
+        <v>2.044082010228518</v>
       </c>
       <c r="F5" t="n">
-        <v>13.02485809901058</v>
+        <v>2.11653944108922</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.43760182592143</v>
+        <v>3.646110296712233</v>
       </c>
       <c r="D6" t="n">
-        <v>22.5203193697912</v>
+        <v>3.659551897591069</v>
       </c>
       <c r="E6" t="n">
-        <v>12.57896621679088</v>
+        <v>2.044082010228518</v>
       </c>
       <c r="F6" t="n">
-        <v>13.02485809901058</v>
+        <v>2.11653944108922</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.68844436891649</v>
+        <v>6.12437220994893</v>
       </c>
       <c r="D7" t="n">
-        <v>28.05006428091776</v>
+        <v>4.558135445649136</v>
       </c>
       <c r="E7" t="n">
-        <v>12.57896621679088</v>
+        <v>2.044082010228518</v>
       </c>
       <c r="F7" t="n">
-        <v>13.02485809901058</v>
+        <v>2.11653944108922</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.06317174598907</v>
+        <v>4.885265408723224</v>
       </c>
       <c r="D8" t="n">
-        <v>30.21824422220158</v>
+        <v>4.910464686107757</v>
       </c>
       <c r="E8" t="n">
-        <v>12.57896621679088</v>
+        <v>2.044082010228518</v>
       </c>
       <c r="F8" t="n">
-        <v>13.02485809901058</v>
+        <v>2.11653944108922</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>43.4422524512352</v>
+        <v>7.05936602332572</v>
       </c>
       <c r="D9" t="n">
-        <v>43.36189602329765</v>
+        <v>7.046308103785868</v>
       </c>
       <c r="E9" t="n">
-        <v>12.57896621679088</v>
+        <v>2.044082010228518</v>
       </c>
       <c r="F9" t="n">
-        <v>13.02485809901058</v>
+        <v>2.11653944108922</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>48.44630133839156</v>
+        <v>7.87252396748863</v>
       </c>
       <c r="D10" t="n">
-        <v>24.13503677229434</v>
+        <v>3.921943475497831</v>
       </c>
       <c r="E10" t="n">
-        <v>12.57896621679088</v>
+        <v>2.044082010228518</v>
       </c>
       <c r="F10" t="n">
-        <v>13.02485809901058</v>
+        <v>2.11653944108922</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>45.3405218839594</v>
+        <v>7.367834806143404</v>
       </c>
       <c r="D11" t="n">
-        <v>45.48153746360126</v>
+        <v>7.390749837835205</v>
       </c>
       <c r="E11" t="n">
-        <v>12.57896621679088</v>
+        <v>2.044082010228518</v>
       </c>
       <c r="F11" t="n">
-        <v>13.02485809901058</v>
+        <v>2.11653944108922</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>53.53665276550743</v>
+        <v>8.699706074394959</v>
       </c>
       <c r="D12" t="n">
-        <v>25.25297684444694</v>
+        <v>4.103608737222627</v>
       </c>
       <c r="E12" t="n">
-        <v>12.57896621679088</v>
+        <v>2.044082010228518</v>
       </c>
       <c r="F12" t="n">
-        <v>13.02485809901058</v>
+        <v>2.11653944108922</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>52.37100758553853</v>
+        <v>8.510288732650011</v>
       </c>
       <c r="D13" t="n">
-        <v>41.91697884203181</v>
+        <v>6.811509061830169</v>
       </c>
       <c r="E13" t="n">
-        <v>12.57896621679088</v>
+        <v>2.044082010228518</v>
       </c>
       <c r="F13" t="n">
-        <v>13.02485809901058</v>
+        <v>2.11653944108922</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>54.80038720425729</v>
+        <v>8.90506292069181</v>
       </c>
       <c r="D14" t="n">
-        <v>54.73912366375059</v>
+        <v>8.895107595359471</v>
       </c>
       <c r="E14" t="n">
-        <v>12.57896621679088</v>
+        <v>2.044082010228518</v>
       </c>
       <c r="F14" t="n">
-        <v>13.02485809901058</v>
+        <v>2.11653944108922</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>46.42291389186853</v>
+        <v>7.543723507428636</v>
       </c>
       <c r="D15" t="n">
-        <v>47.38391562715545</v>
+        <v>7.69988628941276</v>
       </c>
       <c r="E15" t="n">
-        <v>12.57896621679088</v>
+        <v>2.044082010228518</v>
       </c>
       <c r="F15" t="n">
-        <v>13.02485809901058</v>
+        <v>2.11653944108922</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>36.46903110973415</v>
+        <v>5.9262175553318</v>
       </c>
       <c r="D16" t="n">
-        <v>37.23017800110897</v>
+        <v>6.049903925180208</v>
       </c>
       <c r="E16" t="n">
-        <v>12.57896621679088</v>
+        <v>2.044082010228518</v>
       </c>
       <c r="F16" t="n">
-        <v>13.02485809901058</v>
+        <v>2.11653944108922</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>49.90891442081196</v>
+        <v>8.110198593381943</v>
       </c>
       <c r="D17" t="n">
-        <v>50.90921001496179</v>
+        <v>8.272746627431291</v>
       </c>
       <c r="E17" t="n">
-        <v>12.57896621679088</v>
+        <v>2.044082010228518</v>
       </c>
       <c r="F17" t="n">
-        <v>13.02485809901058</v>
+        <v>2.11653944108922</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>51.49963787284995</v>
+        <v>8.368691154338117</v>
       </c>
       <c r="D18" t="n">
-        <v>52.19017971635818</v>
+        <v>8.480904203908205</v>
       </c>
       <c r="E18" t="n">
-        <v>12.57896621679088</v>
+        <v>2.044082010228518</v>
       </c>
       <c r="F18" t="n">
-        <v>13.02485809901058</v>
+        <v>2.11653944108922</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>55.50571584666457</v>
+        <v>9.019678825082993</v>
       </c>
       <c r="D19" t="n">
-        <v>56.32217650615821</v>
+        <v>9.152353682250709</v>
       </c>
       <c r="E19" t="n">
-        <v>12.57896621679088</v>
+        <v>2.044082010228518</v>
       </c>
       <c r="F19" t="n">
-        <v>13.02485809901058</v>
+        <v>2.11653944108922</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
